--- a/MGC_NetSuite_Gap_Summary.xlsx
+++ b/MGC_NetSuite_Gap_Summary.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="95" customHeight="1">
+    <row r="4" ht="110" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -579,23 +579,26 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ลงบัญชี (JE) ครบทุกประเภทสัญญาแล้ว:
-• กลุ่มมีตารางผ่อน: FP, Loan, HP, Leasing, Lease Other
-• กลุ่มภาระผูกพัน: LG/BG, LC, FXF (+ PN, OD, TR)</t>
+          <t>ลงบัญชี (JE) ครบทุกประเภทแล้ว — แบ่ง 3 กลุ่ม:
+• มีตารางผ่อน (on-balance): FP, Loan, HP, Leasing, Lease Other
+• หนี้จริง bullet/revolving (on-balance): PN, OD, TR
+• ภาระผูกพัน (off-balance): LG/BG, LC, FXF</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>กลุ่มภาระผูกพัน (LG/BG, LC, FXF) ตอนนี้ส่งได้แค่ JE
+          <t>เฉพาะกลุ่มภาระผูกพัน off-balance (LG/BG, LC, FXF)
 ยังไม่ได้ส่ง "สรุปยอดภาระผูกพันที่ยังไม่ใช้" ให้ NetSuite
-(เช่น วงเงินค้ำ/รับรองที่ยังเปิดค้างอยู่ — ยอดคงเหลือ)</t>
+(วงเงินค้ำ/รับรองที่ยังเปิดค้าง — ยอดคงเหลือ) · ปัจจุบันมีแต่ JE
+(PN/OD/TR เป็นหนี้จริง ส่ง JE/ยอดปกติ ไม่ใช่ commitment)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>แก้ที่ Flow 3 — แบ่งให้ชัดเป็น 2 กลุ่ม:
+          <t>แก้ Flow 3 — แบ่งให้ชัด:
 (1) มีตารางผ่อน → ส่งตารางงวดเต็ม (FP/Loan/HP/Leasing/Lease Other)
-(2) ภาระผูกพัน → ส่งแค่ประเภท + ยอด (LG/LC/FXF)</t>
+(2) Commitment off-balance → ส่งประเภท + ยอดภาระผูกพัน (LG/BG, LC, FXF)
+PN/OD/TR = หนี้ on-balance ส่ง JE/ยอดตามปกติ ไม่นับเป็น commitment</t>
         </is>
       </c>
     </row>
